--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="personalInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="skills" sheetId="2" r:id="rId2"/>
-    <sheet name="experience" sheetId="3" r:id="rId3"/>
-    <sheet name="projects" sheetId="4" r:id="rId4"/>
-    <sheet name="education" sheetId="5" r:id="rId5"/>
-    <sheet name="githubConfig" sheetId="6" r:id="rId6"/>
+    <sheet name="📋使用说明" sheetId="1" r:id="rId1"/>
+    <sheet name="👤个人信息" sheetId="2" r:id="rId2"/>
+    <sheet name="🎯技能列表" sheetId="3" r:id="rId3"/>
+    <sheet name="🏢工作经历" sheetId="4" r:id="rId4"/>
+    <sheet name="📊项目经历" sheetId="5" r:id="rId5"/>
+    <sheet name="🎓教育背景" sheetId="6" r:id="rId6"/>
+    <sheet name="⚙GitHub配置" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,9 +403,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>desc</v>
+      </c>
+      <c r="C1" t="str">
+        <v>tip</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>📌 整体规则</v>
+      </c>
+      <c r="B2" t="str">
+        <v>修改 Excel 后保存，执行 git 推送即可自动部署</v>
+      </c>
+      <c r="C2" t="str">
+        <v>多条内容用英文分号 ; 分隔（不要用中文分号）</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>👤 个人信息</v>
+      </c>
+      <c r="B4" t="str">
+        <v>personalInfo 表</v>
+      </c>
+      <c r="C4" t="str">
+        <v>直接修改 value 列即可，key 列不要动</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>🎯 技能列表</v>
+      </c>
+      <c r="B5" t="str">
+        <v>skills 表</v>
+      </c>
+      <c r="C5" t="str">
+        <v>每行一条技能；level 填 0-100 的数字；category 必须是以下之一：Frontend / Backend / DevOps &amp; Cloud / Tools &amp; Others</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>🏢 工作经历</v>
+      </c>
+      <c r="B6" t="str">
+        <v>experience 表</v>
+      </c>
+      <c r="C6" t="str">
+        <v>每行一段经历；日期格式 YYYY-MM；多条工作描述/技术栈用 ; 分隔</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>📊 项目经历</v>
+      </c>
+      <c r="B7" t="str">
+        <v>projects 表</v>
+      </c>
+      <c r="C7" t="str">
+        <v>每行一个项目；featured 填 true/false；actions/outcomes/highlights 等多条用 ; 分隔</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>🎓 教育背景</v>
+      </c>
+      <c r="B8" t="str">
+        <v>education 表</v>
+      </c>
+      <c r="C8" t="str">
+        <v>每行一条；category 填：学历教育 / 职业资格 / 培训认证</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>⚙️ GitHub配置</v>
+      </c>
+      <c r="B9" t="str">
+        <v>githubConfig 表</v>
+      </c>
+      <c r="C9" t="str">
+        <v>key-value 格式；languages 特殊格式：名称:百分比:颜色代码; 用 ; 分隔多条</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>🚀 部署命令</v>
+      </c>
+      <c r="B11" t="str">
+        <v>在项目目录执行以下 3 条命令</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v>git add -A</v>
+      </c>
+      <c r="C12" t="str">
+        <v>添加所有修改</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <v>git commit -m "更新简历"</v>
+      </c>
+      <c r="C13" t="str">
+        <v>提交</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v>git -c http.sslBackend=openssl push origin master</v>
+      </c>
+      <c r="C14" t="str">
+        <v>推送到 GitHub（约1分钟后自动部署生效）</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>🌐 访问地址</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://qmar1962-cmd.github.io/interactive-visual-resume/</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B13"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -418,105 +611,113 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>name</v>
+        <v>📝 填写说明</v>
       </c>
       <c r="B2" t="str">
-        <v>陈晓敏</v>
+        <v>只修改右侧「内容」列，左侧「字段名」列不要动</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>title</v>
+        <v>name</v>
       </c>
       <c r="B3" t="str">
-        <v>HRBP / 薪酬绩效资深专家</v>
+        <v>陈晓敏</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>avatarUrl</v>
+        <v>title</v>
       </c>
       <c r="B4" t="str">
-        <v>https://images.unsplash.com/photo-1573496359142-b8d87734a5a2?auto=format&amp;fit=crop&amp;q=80&amp;w=200&amp;h=200</v>
+        <v>HRBP / 薪酬绩效资深专家</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>email</v>
+        <v>avatarUrl</v>
       </c>
       <c r="B5" t="str">
-        <v>xiaomin.chen_hr@example.com</v>
+        <v>https://images.unsplash.com/photo-1573496359142-b8d87734a5a2?auto=format&amp;fit=crop&amp;q=80&amp;w=200&amp;h=200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>phone</v>
+        <v>email</v>
       </c>
       <c r="B6" t="str">
-        <v>138-1234-5678</v>
+        <v>xiaomin.chen_hr@example.com</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>location</v>
+        <v>phone</v>
       </c>
       <c r="B7" t="str">
-        <v>中国 · 深圳</v>
+        <v>138-1234-5678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>website</v>
+        <v>location</v>
       </c>
       <c r="B8" t="str">
-        <v>https://xiaomin-hrbp.github.io</v>
+        <v>中国 · 深圳</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>github</v>
+        <v>website</v>
       </c>
       <c r="B9" t="str">
-        <v>xiaomin-hrbp</v>
+        <v>https://xiaomin-hrbp.github.io</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>linkedin</v>
+        <v>github</v>
       </c>
       <c r="B10" t="str">
-        <v>xiaomin-chen-hr</v>
+        <v>xiaomin-hrbp</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bio</v>
+        <v>linkedin</v>
       </c>
       <c r="B11" t="str">
-        <v>拥有 10 年+ 知名高成长科技企业及跨国集团深厚人力资源管理经验。专注于薪酬福利体系设计 (C&amp;B)、全面绩效激励闭环管理（OKR/KPI/三阶评估）以及业务合作伙伴 (HRBP) 战略落地。擅长将企业经营指标与人效分析指标深度绑定，通过精益调薪策略、宽带薪酬、多元激励以及人效诊断为业务部门打造高产出战队。</v>
+        <v>xiaomin-chen-hr</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>bio</v>
+      </c>
+      <c r="B12" t="str">
+        <v>拥有 10 年+ 知名高成长科技企业及跨国集团深厚人力资源管理经验。专注于薪酬福利体系设计 (C&amp;B)、全面绩效激励闭环管理（OKR/KPI/三阶评估）以及业务合作伙伴 (HRBP) 战略落地。擅长将企业经营指标与人效分析指标深度绑定，通过精益调薪策略、宽带薪酬、多元激励以及人效诊断为业务部门打造高产出战队。</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>summary</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B13" t="str">
         <v>高级人力资源管理师、资深 HRBP 专家。熟谙宽带薪酬、美世/海氏等标杆岗位技能要素评估体系，主导过多次覆盖千人规模的调薪与期权激励方案统筹；深挖业务核心痛点并进行组织重构设计与核心骨干盘点，具备极强的人效数据分析（People Analytics）与信息化 HR 治理工具落地应用能力。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
   </cols>
@@ -537,55 +738,55 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>宽带薪酬与定岗定级体系设计</v>
-      </c>
-      <c r="B2">
-        <v>96</v>
+        <v>📝 分类说明: Frontend=薪酬福利规划(C&amp;B) | Backend=HRBP业务协同 | DevOps &amp; Cloud=组织效能与绩效激活 | Tools &amp; Others=人力数字化与用工合规</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Frontend</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>全面绩效闭环与动态激励机制 (OKR/KPI)</v>
+        <v>宽带薪酬与定岗定级体系设计</v>
       </c>
       <c r="B3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" t="str">
         <v>Frontend</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>人工成本预算分析与总数控制 (C&amp;B Control)</v>
+        <v>全面绩效闭环与动态激励机制 (OKR/KPI)</v>
       </c>
       <c r="B4">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" t="str">
         <v>Frontend</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HRBP 业务诊断与组织痛点攻坚</v>
+        <v>人工成本预算分析与总数控制 (C&amp;B Control)</v>
       </c>
       <c r="B5">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C5" t="str">
-        <v>Backend</v>
+        <v>Frontend</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -593,511 +794,369 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>组织架构重建与核心岗位对标设计</v>
+        <v>HRBP 业务诊断与组织痛点攻坚</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C6" t="str">
         <v>Backend</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>核心干部后备梯队盘点 (Succession Planning)</v>
+        <v>组织架构重建与核心岗位对标设计</v>
       </c>
       <c r="B7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="str">
         <v>Backend</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>组织效能盘点与综合人效分析 (ROI &amp; L&amp;D)</v>
+        <v>核心干部后备梯队盘点 (Succession Planning)</v>
       </c>
       <c r="B8">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C8" t="str">
-        <v>DevOps &amp; Cloud</v>
+        <v>Backend</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>360度环评胜任力建模与反馈机制</v>
+        <v>组织效能盘点与综合人效分析 (ROI &amp; L&amp;D)</v>
       </c>
       <c r="B9">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C9" t="str">
         <v>DevOps &amp; Cloud</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>核心骨干定制激励与个人发展计划 (IDP)</v>
+        <v>360度环评胜任力建模与反馈机制</v>
       </c>
       <c r="B10">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C10" t="str">
         <v>DevOps &amp; Cloud</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>高级数据管理与决策透析 (Excel/PowerBI/SQL)</v>
+        <v>核心骨干定制激励与个人发展计划 (IDP)</v>
       </c>
       <c r="B11">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C11" t="str">
-        <v>Tools &amp; Others</v>
+        <v>DevOps &amp; Cloud</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>一体化数智 HRM 与飞书 OKR 系统集成</v>
+        <v>高级数据管理与决策透析 (Excel/PowerBI/SQL)</v>
       </c>
       <c r="B12">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12" t="str">
         <v>Tools &amp; Others</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>劳动纠纷防范与用工风险实务管理</v>
+        <v>一体化数智 HRM 与飞书 OKR 系统集成</v>
       </c>
       <c r="B13">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C13" t="str">
         <v>Tools &amp; Others</v>
       </c>
       <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>劳动纠纷防范与用工风险实务管理</v>
+      </c>
+      <c r="B14">
+        <v>86</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Tools &amp; Others</v>
+      </c>
+      <c r="D14">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="80.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>company</v>
-      </c>
-      <c r="C1" t="str">
-        <v>role</v>
-      </c>
-      <c r="D1" t="str">
-        <v>startDate</v>
-      </c>
-      <c r="E1" t="str">
-        <v>endDate</v>
-      </c>
-      <c r="F1" t="str">
-        <v>location</v>
-      </c>
-      <c r="G1" t="str">
-        <v>description</v>
-      </c>
-      <c r="H1" t="str">
-        <v>techStack</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>exp_1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>领航创想智能科技有限公司</v>
-      </c>
-      <c r="C2" t="str">
-        <v>资深 HRBP 专家 / 薪酬绩效部负责人</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2022-04</v>
-      </c>
-      <c r="E2" t="str">
-        <v>至今</v>
-      </c>
-      <c r="F2" t="str">
-        <v>深圳</v>
-      </c>
-      <c r="G2" t="str">
-        <v>深度服务于千人级产研、运营及全球业务群。主导重构并落定了2023-2025年最新集团宽带薪酬标准和定岗定级总盘子，方案升级后，研发核心高价值人才流失率同比大幅缩减 35%。;打通'战略-绩效-激励'闭环，推行'OKR + 敏捷KPI双轨考核制'。协同产品线总裁重整核心业务提成与奖金分配政策，直接促成组织人效提升 18%，单兵销售业绩复合增长 22%。;联合数据团队从零构建'集团人效效能分析管理系统 (People Analytics Console)'，深度集成飞书与配薪核算引擎，实时打通人工成本支出额、编制冗余度、及绩效饱和度，为集团管委会决策提供精确数据依据。</v>
-      </c>
-      <c r="H2" t="str">
-        <v>全面薪酬宽带管理 (C&amp;B);组织架构重组;OKR/KPI 双轨考核制;人效看板 (BI);飞书HRM;中高管绩效辅导</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>exp_2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>极光数字空间科技有限公司</v>
-      </c>
-      <c r="C3" t="str">
-        <v>HRBP 经理 (产研事业部负责人)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2018-09</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2022-03</v>
-      </c>
-      <c r="F3" t="str">
-        <v>深圳</v>
-      </c>
-      <c r="G3" t="str">
-        <v>全面负责技术中心（450人+）的组织发展、人才梯队与激励配置工作。主导中高层核心中坚力量两轮大盘点，并对核心核心架构师及骨干实施'一人一策'动态股权保留政策，使核心技术专家留任率提升至 95%。;深入业务核心开展敏捷改组，剥离重叠的多维繁冗层级，重组为 8 个高内聚自闭环业务战队，大幅提升内部业务流转与人效提速 15%。;推行月度人效专项复盘、新晋技术经理管理辅导；协同集团年度薪酬回顾，解决历史不匹配倒挂等痛点，年度调薪满意度评分达 4.8 / 5.0。</v>
-      </c>
-      <c r="H3" t="str">
-        <v>HRBP 实践;胜任力模型评估;晋升评审机制;晋升调薪测算模型;组织诊断与人效分析</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>exp_3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>中科智能制造控股集团</v>
-      </c>
-      <c r="C4" t="str">
-        <v>人力资源主管 -&gt; 薪酬福利高级专员</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2015-07</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2018-08</v>
-      </c>
-      <c r="F4" t="str">
-        <v>上海</v>
-      </c>
-      <c r="G4" t="str">
-        <v>统管 2000+ 关系复杂中大型组织员工算薪、多层级社保公积金及个税代扣代缴事宜，流程精密核算，创下连续 12 季度 100% 算薪'零差错'。;深度协助美世（Mercer）岗位对标盘点咨询项目，作为项目主力撰写与对标 150 余个核心中高层及技术研发关键岗位说明书；协同定制《集团薪酬福利精益发放白皮书》，极大降低不规避福利成本支出。</v>
-      </c>
-      <c r="H4" t="str">
-        <v>海氏/美世岗位对标;精密个税社保算薪实务;用工风险管理;组织绩效模型;高级 Excel 分析建模</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:H5"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="50.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
-    <col min="12" max="12" width="50.83203125" customWidth="1"/>
-    <col min="13" max="13" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="80.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>title</v>
+        <v>company</v>
       </c>
       <c r="C1" t="str">
+        <v>role</v>
+      </c>
+      <c r="D1" t="str">
+        <v>startDate</v>
+      </c>
+      <c r="E1" t="str">
+        <v>endDate</v>
+      </c>
+      <c r="F1" t="str">
+        <v>location</v>
+      </c>
+      <c r="G1" t="str">
         <v>description</v>
       </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>featured</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>techStack</v>
       </c>
-      <c r="G1" t="str">
-        <v>role</v>
-      </c>
-      <c r="H1" t="str">
-        <v>timeline</v>
-      </c>
-      <c r="I1" t="str">
-        <v>background</v>
-      </c>
-      <c r="J1" t="str">
-        <v>objective</v>
-      </c>
-      <c r="K1" t="str">
-        <v>actions</v>
-      </c>
-      <c r="L1" t="str">
-        <v>outcomes</v>
-      </c>
-      <c r="M1" t="str">
-        <v>highlights</v>
-      </c>
-    </row>
-    <row r="2">
+    </row>
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" t="str">
-        <v>proj_1</v>
+        <v>📝 提示</v>
       </c>
       <c r="B2" t="str">
-        <v>最新年度全集团宽带薪酬重构及动态绩效挂钩计划</v>
+        <v>日期格式: YYYY-MM（如 2022-04）</v>
       </c>
       <c r="C2" t="str">
-        <v>针对原有薪金重合严重、职级虚高、起步倒挂等历史痛点，主导落地的涵盖千人规模的宽带薪酬重新评估定档和调薪算法项目。</v>
+        <v>至今填: 至今</v>
       </c>
       <c r="D2" t="str">
-        <v>薪酬福利核心工程</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>宽带薪酬;调薪矩阵算法;美世定档模型;Excel 仿真财务模型</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>项目负责人</v>
+        <v>多条工作描述用英文分号 ; 隔开</v>
       </c>
       <c r="H2" t="str">
-        <v>2023-2024</v>
-      </c>
-      <c r="I2" t="str">
-        <v>原有薪酬体系存在薪金重合严重、职级虚高、起步倒挂等历史痛点，导致核心人才流失率高、调薪满意度低，亟需系统性重构。</v>
-      </c>
-      <c r="J2" t="str">
-        <v>在把控总人本支出增幅低于5%的前提下，激活绩优主力团队，同时消除历史倒挂问题。</v>
-      </c>
-      <c r="K2" t="str">
-        <v>搭建深度仿真数学测算，推演12种不同调薪分配曲线，量化分析每种方案的成本影响与激励效果。;引入美世（Mercer）岗位要素评估体系，对全集团核心岗位重新定档定级。;设计晋升定级和薪资起锚点的自动锁定矩阵，实现调薪流程标准化与自动化。</v>
-      </c>
-      <c r="L2" t="str">
-        <v>在把控总人本支出增幅低于5%的同时，高质激活了前40%的绩优主力团队。;将历史倒挂严重性由25%压缩至2.5%以内。;研发核心高价值人才流失率同比大幅缩减35%。</v>
-      </c>
-      <c r="M2" t="str">
-        <v>搭建深度仿真数学测算，推演 12 种不同调薪分配曲线，最终实现在把控总人本支出增幅低于 5% 的同时，高质激活了前 40% 的绩优主力团队。;重置新晋升定级和薪资起锚点的自动锁定矩阵，将历史倒挂严重性由 25% 压缩至 2.5% 以内。</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>多条技能标签用英文分号 ; 隔开</v>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" t="str">
-        <v>proj_2</v>
+        <v>exp_1</v>
       </c>
       <c r="B3" t="str">
-        <v>HR 人效数据飞轮与"一站式人效监控 BI 决策平台"</v>
+        <v>领航创想智能科技有限公司</v>
       </c>
       <c r="C3" t="str">
-        <v>自研一套与飞书多维表格与 PowerBI 打通的组织效能监控系统，用于全息透视实时人员编制、主动流失、业绩 ROI、单兵创出以及绩效偏离系数。</v>
+        <v>资深 HRBP 专家 / 薪酬绩效部负责人</v>
       </c>
       <c r="D3" t="str">
-        <v>人力资源数字化</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+        <v>2022-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v>至今</v>
       </c>
       <c r="F3" t="str">
-        <v>PowerBI;People Analytics;数据清洗;指标库治理;飞书 API</v>
+        <v>深圳</v>
       </c>
       <c r="G3" t="str">
-        <v>项目负责人</v>
+        <v>深度服务于千人级产研、运营及全球业务群。主导重构并落定了2023-2025年最新集团宽带薪酬标准和定岗定级总盘子，方案升级后，研发核心高价值人才流失率同比大幅缩减 35%。;打通'战略-绩效-激励'闭环，推行'OKR + 敏捷KPI双轨考核制'。协同产品线总裁重整核心业务提成与奖金分配政策，直接促成组织人效提升 18%，单兵销售业绩复合增长 22%。;联合数据团队从零构建'集团人效效能分析管理系统 (People Analytics Console)'，深度集成飞书与配薪核算引擎，实时打通人工成本支出额、编制冗余度、及绩效饱和度，为集团管委会决策提供精确数据依据。</v>
       </c>
       <c r="H3" t="str">
-        <v>2023-2024</v>
-      </c>
-      <c r="I3" t="str">
-        <v>传统人力数据统计依赖手工跨源取数，效率低下且时效性差，管理层无法实时获取人效数据支撑决策。</v>
-      </c>
-      <c r="J3" t="str">
-        <v>将人效数据从手工两周合并一次升级为日级自动抓取，构建实时组织效能监控与预警体系。</v>
-      </c>
-      <c r="K3" t="str">
-        <v>打通飞书多维表格与PowerBI数据流，建立自动化数据采集与清洗管道。;设计组织效能指标库，涵盖人员编制、主动流失率、业绩ROI、单兵产出、绩效偏离系数等核心维度。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标等智能预警模型。</v>
-      </c>
-      <c r="L3" t="str">
-        <v>将传统手工跨源取数及算账时间从两周合并一次缩短至日级自动抓取更新，人力统计生产力提升95%。;帮助管理层提早识别并化解多起用工重叠危机，避免潜在成本损失。;实时数据看板覆盖全集团，管委会决策响应速度提升3倍。</v>
-      </c>
-      <c r="M3" t="str">
-        <v>将传统手工跨源取数及算账的时间从原本每两周合并一次缩短至日级自动抓取更新，提高人力资源统计生产力达 95%。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标，帮助管理层提早识别并化解了多起用工重叠危机。</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>全面薪酬宽带管理 (C&amp;B);组织架构重组;OKR/KPI 双轨考核制;人效看板 (BI);飞书HRM;中高管绩效辅导</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" t="str">
-        <v>proj_3</v>
+        <v>exp_2</v>
       </c>
       <c r="B4" t="str">
-        <v>产研核心主管 360 度能力盘点与"主管成长加速营"</v>
+        <v>极光数字空间科技有限公司</v>
       </c>
       <c r="C4" t="str">
-        <v>针对产研事业部中层管理者管理成熟度参差不齐的问题，引入针对性的 360 度胜任力矩阵全方位诊断，并配套设计出 IDP (个人成长计划) 落地赋能方案。</v>
+        <v>HRBP 经理 (产研事业部负责人)</v>
       </c>
       <c r="D4" t="str">
-        <v>组织能力盘点及发展</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
+        <v>2018-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2022-03</v>
       </c>
       <c r="F4" t="str">
-        <v>360度评估机制;胜任力九宫格;IDP 提升路线;管理者角色转身辅导</v>
+        <v>深圳</v>
       </c>
       <c r="G4" t="str">
-        <v>项目负责人</v>
+        <v>全面负责技术中心（450人+）的组织发展、人才梯队与激励配置工作。主导中高层核心中坚力量两轮大盘点，并对核心核心架构师及骨干实施'一人一策'动态股权保留政策，使核心技术专家留任率提升至 95%。;深入业务核心开展敏捷改组，剥离重叠的多维繁冗层级，重组为 8 个高内聚自闭环业务战队，大幅提升内部业务流转与人效提速 15%。;推行月度人效专项复盘、新晋技术经理管理辅导；协同集团年度薪酬回顾，解决历史不匹配倒挂等痛点，年度调薪满意度评分达 4.8 / 5.0。</v>
       </c>
       <c r="H4" t="str">
-        <v>2022-2023</v>
-      </c>
-      <c r="I4" t="str">
-        <v>产研事业部中层管理者管理成熟度参差不齐，基层工程师与管理者沟通割裂，内部继任准备度不足。</v>
-      </c>
-      <c r="J4" t="str">
-        <v>通过360度胜任力诊断精准定位管理短板，配套IDP个人成长计划与加速营，提升内部继任准备度。</v>
-      </c>
-      <c r="K4" t="str">
-        <v>引入360度胜任力矩阵，对80+中高级经理进行全方位能力诊断与盘点。;基于诊断结果，为核心高潜人才设计'一人一策'IDP个人发展计划。;配套两场'管理者角色转身理论与研讨'，聚焦沟通力与团队领导力提升。</v>
-      </c>
-      <c r="L4" t="str">
-        <v>高标准全票落地80+中高级经理能力诊断，构建核心高潜力人才蓄水池。;组织'内部继任准备度'实质性提升40%。;基层工程师与管理者沟通满意度显著改善。</v>
-      </c>
-      <c r="M4" t="str">
-        <v>高标准全票落地 80+ 中高级经理能力诊断，构建集团核心高潜力人才蓄水池，使组织'内部继任准备度'实质提升 40%。;配套两场'管理者角色转身理论与研讨'，切实改善了产研线基层工程师与管理者之间原本割裂的沟通习惯。</v>
+        <v>HRBP 实践;胜任力模型评估;晋升评审机制;晋升调薪测算模型;组织诊断与人效分析</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>exp_3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>中科智能制造控股集团</v>
+      </c>
+      <c r="C5" t="str">
+        <v>人力资源主管 -&gt; 薪酬福利高级专员</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2015-07</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2018-08</v>
+      </c>
+      <c r="F5" t="str">
+        <v>上海</v>
+      </c>
+      <c r="G5" t="str">
+        <v>统管 2000+ 关系复杂中大型组织员工算薪、多层级社保公积金及个税代扣代缴事宜，流程精密核算，创下连续 12 季度 100% 算薪'零差错'。;深度协助美世（Mercer）岗位对标盘点咨询项目，作为项目主力撰写与对标 150 余个核心中高层及技术研发关键岗位说明书；协同定制《集团薪酬福利精益发放白皮书》，极大降低不规避福利成本支出。</v>
+      </c>
+      <c r="H5" t="str">
+        <v>海氏/美世岗位对标;精密个税社保算薪实务;用工风险管理;组织绩效模型;高级 Excel 分析建模</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M5"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="45.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="11" max="11" width="55.83203125" customWidth="1"/>
+    <col min="12" max="12" width="55.83203125" customWidth="1"/>
+    <col min="13" max="13" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>institution</v>
+        <v>title</v>
       </c>
       <c r="C1" t="str">
-        <v>degree</v>
+        <v>category</v>
       </c>
       <c r="D1" t="str">
-        <v>major</v>
+        <v>featured</v>
       </c>
       <c r="E1" t="str">
-        <v>startDate</v>
+        <v>role</v>
       </c>
       <c r="F1" t="str">
-        <v>endDate</v>
+        <v>timeline</v>
       </c>
       <c r="G1" t="str">
-        <v>category</v>
+        <v>description</v>
       </c>
       <c r="H1" t="str">
-        <v>certName</v>
+        <v>background</v>
       </c>
       <c r="I1" t="str">
-        <v>certOrg</v>
+        <v>objective</v>
       </c>
       <c r="J1" t="str">
-        <v>certDate</v>
+        <v>actions</v>
       </c>
       <c r="K1" t="str">
+        <v>outcomes</v>
+      </c>
+      <c r="L1" t="str">
         <v>highlights</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="M1" t="str">
+        <v>techStack</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" t="str">
-        <v>edu_1</v>
+        <v>📝 提示</v>
       </c>
       <c r="B2" t="str">
-        <v>中南财经政法大学</v>
+        <v>featured 填 true 或 false</v>
       </c>
       <c r="C2" t="str">
-        <v>本科</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>人力资源管理</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>2011-09</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>2015-06</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>学历教育</v>
+        <v>多条内容用英文分号 ; 隔开</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -1109,19 +1168,277 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>主修组织行为学、薪酬福利设计、绩效考评与实务、劳动法与合同合规规划。;曾荣获国家级励志奖学金、校级优秀毕业生。毕设《互联网科技企业动态期权及虚拟股绩效绑定设计》被评为校级一等论文。</v>
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="str">
+        <v>proj_1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>最新年度全集团宽带薪酬重构及动态绩效挂钩计划</v>
+      </c>
+      <c r="C3" t="str">
+        <v>薪酬福利核心工程</v>
+      </c>
+      <c r="D3" t="str">
+        <v>true</v>
+      </c>
+      <c r="E3" t="str">
+        <v>项目负责人</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2023-2024</v>
+      </c>
+      <c r="G3" t="str">
+        <v>针对原有薪金重合严重、职级虚高、起步倒挂等历史痛点，主导落地的涵盖千人规模的宽带薪酬重新评估定档和调薪算法项目。</v>
+      </c>
+      <c r="H3" t="str">
+        <v>原有薪酬体系存在薪金重合严重、职级虚高、起步倒挂等历史痛点，导致核心人才流失率高、调薪满意度低，亟需系统性重构。</v>
+      </c>
+      <c r="I3" t="str">
+        <v>在把控总人本支出增幅低于5%的前提下，激活绩优主力团队，同时消除历史倒挂问题。</v>
+      </c>
+      <c r="J3" t="str">
+        <v>搭建深度仿真数学测算，推演12种不同调薪分配曲线，量化分析每种方案的成本影响与激励效果。;引入美世（Mercer）岗位要素评估体系，对全集团核心岗位重新定档定级。;设计晋升定级和薪资起锚点的自动锁定矩阵，实现调薪流程标准化与自动化。</v>
+      </c>
+      <c r="K3" t="str">
+        <v>在把控总人本支出增幅低于5%的同时，高质激活了前40%的绩优主力团队。;将历史倒挂严重性由25%压缩至2.5%以内。;研发核心高价值人才流失率同比大幅缩减35%。</v>
+      </c>
+      <c r="L3" t="str">
+        <v>搭建深度仿真数学测算，推演 12 种不同调薪分配曲线，最终实现在把控总人本支出增幅低于 5% 的同时，高质激活了前 40% 的绩优主力团队。;重置新晋升定级和薪资起锚点的自动锁定矩阵，将历史倒挂严重性由 25% 压缩至 2.5% 以内。</v>
+      </c>
+      <c r="M3" t="str">
+        <v>宽带薪酬;调薪矩阵算法;美世定档模型;Excel 仿真财务模型</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="str">
+        <v>proj_2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HR 人效数据飞轮与"一站式人效监控 BI 决策平台"</v>
+      </c>
+      <c r="C4" t="str">
+        <v>人力资源数字化</v>
+      </c>
+      <c r="D4" t="str">
+        <v>true</v>
+      </c>
+      <c r="E4" t="str">
+        <v>项目负责人</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2023-2024</v>
+      </c>
+      <c r="G4" t="str">
+        <v>自研一套与飞书多维表格与 PowerBI 打通的组织效能监控系统，用于全息透视实时人员编制、主动流失、业绩 ROI、单兵创出以及绩效偏离系数。</v>
+      </c>
+      <c r="H4" t="str">
+        <v>传统人力数据统计依赖手工跨源取数，效率低下且时效性差，管理层无法实时获取人效数据支撑决策。</v>
+      </c>
+      <c r="I4" t="str">
+        <v>将人效数据从手工两周合并一次升级为日级自动抓取，构建实时组织效能监控与预警体系。</v>
+      </c>
+      <c r="J4" t="str">
+        <v>打通飞书多维表格与PowerBI数据流，建立自动化数据采集与清洗管道。;设计组织效能指标库，涵盖人员编制、主动流失率、业绩ROI、单兵产出、绩效偏离系数等核心维度。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标等智能预警模型。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>将传统手工跨源取数及算账时间从两周合并一次缩短至日级自动抓取更新，人力统计生产力提升95%。;帮助管理层提早识别并化解多起用工重叠危机，避免潜在成本损失。;实时数据看板覆盖全集团，管委会决策响应速度提升3倍。</v>
+      </c>
+      <c r="L4" t="str">
+        <v>将传统手工跨源取数及算账的时间从原本每两周合并一次缩短至日级自动抓取更新，提高人力资源统计生产力达 95%。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标，帮助管理层提早识别并化解了多起用工重叠危机。</v>
+      </c>
+      <c r="M4" t="str">
+        <v>PowerBI;People Analytics;数据清洗;指标库治理;飞书 API</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>proj_3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>产研核心主管 360 度能力盘点与"主管成长加速营"</v>
+      </c>
+      <c r="C5" t="str">
+        <v>组织能力盘点及发展</v>
+      </c>
+      <c r="D5" t="str">
+        <v>false</v>
+      </c>
+      <c r="E5" t="str">
+        <v>项目负责人</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2022-2023</v>
+      </c>
+      <c r="G5" t="str">
+        <v>针对产研事业部中层管理者管理成熟度参差不齐的问题，引入针对性的 360 度胜任力矩阵全方位诊断，并配套设计出 IDP (个人成长计划) 落地赋能方案。</v>
+      </c>
+      <c r="H5" t="str">
+        <v>产研事业部中层管理者管理成熟度参差不齐，基层工程师与管理者沟通割裂，内部继任准备度不足。</v>
+      </c>
+      <c r="I5" t="str">
+        <v>通过360度胜任力诊断精准定位管理短板，配套IDP个人成长计划与加速营，提升内部继任准备度。</v>
+      </c>
+      <c r="J5" t="str">
+        <v>引入360度胜任力矩阵，对80+中高级经理进行全方位能力诊断与盘点。;基于诊断结果，为核心高潜人才设计'一人一策'IDP个人发展计划。;配套两场'管理者角色转身理论与研讨'，聚焦沟通力与团队领导力提升。</v>
+      </c>
+      <c r="K5" t="str">
+        <v>高标准全票落地80+中高级经理能力诊断，构建核心高潜力人才蓄水池。;组织'内部继任准备度'实质性提升40%。;基层工程师与管理者沟通满意度显著改善。</v>
+      </c>
+      <c r="L5" t="str">
+        <v>高标准全票落地 80+ 中高级经理能力诊断，构建集团核心高潜力人才蓄水池，使组织'内部继任准备度'实质提升 40%。;配套两场'管理者角色转身理论与研讨'，切实改善了产研线基层工程师与管理者之间原本割裂的沟通习惯。</v>
+      </c>
+      <c r="M5" t="str">
+        <v>360度评估机制;胜任力九宫格;IDP 提升路线;管理者角色转身辅导</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:K3"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="55.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>category</v>
+      </c>
+      <c r="C1" t="str">
+        <v>institution</v>
+      </c>
+      <c r="D1" t="str">
+        <v>degree</v>
+      </c>
+      <c r="E1" t="str">
+        <v>major</v>
+      </c>
+      <c r="F1" t="str">
+        <v>startDate</v>
+      </c>
+      <c r="G1" t="str">
+        <v>endDate</v>
+      </c>
+      <c r="H1" t="str">
+        <v>certName</v>
+      </c>
+      <c r="I1" t="str">
+        <v>certOrg</v>
+      </c>
+      <c r="J1" t="str">
+        <v>certDate</v>
+      </c>
+      <c r="K1" t="str">
+        <v>highlights</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>📝 提示</v>
+      </c>
+      <c r="B2" t="str">
+        <v>填: 学历教育/职业资格/培训认证</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>格式: YYYY-MM</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>职业资格/培训认证时填写</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>edu_1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>学历教育</v>
+      </c>
+      <c r="C3" t="str">
+        <v>中南财经政法大学</v>
+      </c>
+      <c r="D3" t="str">
+        <v>本科</v>
+      </c>
+      <c r="E3" t="str">
+        <v>人力资源管理</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2011-09</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2015-06</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>主修组织行为学、薪酬福利设计、绩效考评与实务、劳动法与合同合规规划。;曾荣获国家级励志奖学金、校级优秀毕业生。毕设《互联网科技企业动态期权及虚拟股绩效绑定设计》被评为校级一等论文。</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="80.83203125" customWidth="1"/>
@@ -1137,55 +1454,63 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>username</v>
+        <v>📝 填写说明</v>
       </c>
       <c r="B2" t="str">
-        <v>xiaomin-hrbp</v>
+        <v>只修改右侧「值」列，左侧「配置项」列不要动</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>useLiveApi</v>
+        <v>username</v>
       </c>
       <c r="B3" t="str">
-        <v>false</v>
+        <v>xiaomin-hrbp</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>repoCountOverride</v>
+        <v>useLiveApi</v>
       </c>
       <c r="B4" t="str">
-        <v>12</v>
+        <v>false</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>commitCountOverride</v>
+        <v>repoCountOverride</v>
       </c>
       <c r="B5" t="str">
-        <v>184</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>starredCountOverride</v>
+        <v>commitCountOverride</v>
       </c>
       <c r="B6" t="str">
-        <v>45</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>starredCountOverride</v>
+      </c>
+      <c r="B7" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>languages</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B8" t="str">
         <v>薪酬福利设计与规划 (C&amp;B):38.5:#10b981;全面绩效激励机制对齐 (KPI/OKR):28.2:#3b82f6;HRBP 业务诊断与组织发展 (OD):18.3:#f59e0b;人效效能分析系统 (BI &amp; Analytics):10.0:#8b5cf6;劳动合同合规与用工风险预防:5.0:#ef4444</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -405,20 +405,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>section</v>
+        <v>模块</v>
       </c>
       <c r="B1" t="str">
-        <v>desc</v>
+        <v>说明</v>
       </c>
       <c r="C1" t="str">
-        <v>tip</v>
+        <v>填写提示</v>
       </c>
     </row>
     <row r="2">
@@ -448,10 +448,10 @@
         <v>👤 个人信息</v>
       </c>
       <c r="B4" t="str">
-        <v>personalInfo 表</v>
+        <v>个人信息表</v>
       </c>
       <c r="C4" t="str">
-        <v>直接修改 value 列即可，key 列不要动</v>
+        <v>只改「内容」列，别动「字段名」列</v>
       </c>
     </row>
     <row r="5">
@@ -459,10 +459,10 @@
         <v>🎯 技能列表</v>
       </c>
       <c r="B5" t="str">
-        <v>skills 表</v>
+        <v>技能表</v>
       </c>
       <c r="C5" t="str">
-        <v>每行一条技能；level 填 0-100 的数字；category 必须是以下之一：Frontend / Backend / DevOps &amp; Cloud / Tools &amp; Others</v>
+        <v>每行一条；熟练度填 0-100；分类填：薪酬福利规划 / HRBP业务协同 / 组织效能与绩效激活 / 人力数字化与用工合规</v>
       </c>
     </row>
     <row r="6">
@@ -470,10 +470,10 @@
         <v>🏢 工作经历</v>
       </c>
       <c r="B6" t="str">
-        <v>experience 表</v>
+        <v>工作经历表</v>
       </c>
       <c r="C6" t="str">
-        <v>每行一段经历；日期格式 YYYY-MM；多条工作描述/技术栈用 ; 分隔</v>
+        <v>每行一段经历；日期格式 YYYY-MM；多条描述/标签用 ; 分隔</v>
       </c>
     </row>
     <row r="7">
@@ -481,10 +481,10 @@
         <v>📊 项目经历</v>
       </c>
       <c r="B7" t="str">
-        <v>projects 表</v>
+        <v>项目表</v>
       </c>
       <c r="C7" t="str">
-        <v>每行一个项目；featured 填 true/false；actions/outcomes/highlights 等多条用 ; 分隔</v>
+        <v>每行一个项目；是否重点填 是/否；多条内容用 ; 分隔</v>
       </c>
     </row>
     <row r="8">
@@ -492,10 +492,10 @@
         <v>🎓 教育背景</v>
       </c>
       <c r="B8" t="str">
-        <v>education 表</v>
+        <v>教育表</v>
       </c>
       <c r="C8" t="str">
-        <v>每行一条；category 填：学历教育 / 职业资格 / 培训认证</v>
+        <v>每行一条；类别填：学历教育 / 职业资格 / 培训认证</v>
       </c>
     </row>
     <row r="9">
@@ -503,10 +503,10 @@
         <v>⚙️ GitHub配置</v>
       </c>
       <c r="B9" t="str">
-        <v>githubConfig 表</v>
+        <v>展示面板数据</v>
       </c>
       <c r="C9" t="str">
-        <v>key-value 格式；languages 特殊格式：名称:百分比:颜色代码; 用 ; 分隔多条</v>
+        <v>只改「值」列，别动「配置项」列</v>
       </c>
     </row>
     <row r="10">
@@ -597,16 +597,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B13"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>key</v>
+        <v>字段名（勿改）</v>
       </c>
       <c r="B1" t="str">
-        <v>value</v>
+        <v>内容（请修改这里）</v>
       </c>
     </row>
     <row r="2">
@@ -614,7 +614,7 @@
         <v>📝 填写说明</v>
       </c>
       <c r="B2" t="str">
-        <v>只修改右侧「内容」列，左侧「字段名」列不要动</v>
+        <v>只修改本列，左侧字段名列不要动</v>
       </c>
     </row>
     <row r="3">
@@ -716,29 +716,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D14"/>
   <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>name</v>
+        <v>技能名称</v>
       </c>
       <c r="B1" t="str">
-        <v>level</v>
+        <v>熟练度(0-100)</v>
       </c>
       <c r="C1" t="str">
-        <v>category</v>
+        <v>分类</v>
       </c>
       <c r="D1" t="str">
-        <v>yearsOfExp</v>
+        <v>经验年限</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>📝 分类说明: Frontend=薪酬福利规划(C&amp;B) | Backend=HRBP业务协同 | DevOps &amp; Cloud=组织效能与绩效激活 | Tools &amp; Others=人力数字化与用工合规</v>
+        <v>📝 分类对照: 薪酬福利规划=Frontend | HRBP业务协同=Backend | 组织效能与绩效激活=DevOps &amp; Cloud | 人力数字化与用工合规=Tools &amp; Others</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -758,7 +758,7 @@
         <v>96</v>
       </c>
       <c r="C3" t="str">
-        <v>Frontend</v>
+        <v>薪酬福利规划</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -772,7 +772,7 @@
         <v>95</v>
       </c>
       <c r="C4" t="str">
-        <v>Frontend</v>
+        <v>薪酬福利规划</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -786,7 +786,7 @@
         <v>92</v>
       </c>
       <c r="C5" t="str">
-        <v>Frontend</v>
+        <v>薪酬福利规划</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -800,7 +800,7 @@
         <v>94</v>
       </c>
       <c r="C6" t="str">
-        <v>Backend</v>
+        <v>HRBP业务协同</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -814,7 +814,7 @@
         <v>90</v>
       </c>
       <c r="C7" t="str">
-        <v>Backend</v>
+        <v>HRBP业务协同</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -828,7 +828,7 @@
         <v>88</v>
       </c>
       <c r="C8" t="str">
-        <v>Backend</v>
+        <v>HRBP业务协同</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>93</v>
       </c>
       <c r="C9" t="str">
-        <v>DevOps &amp; Cloud</v>
+        <v>组织效能与绩效激活</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -856,7 +856,7 @@
         <v>88</v>
       </c>
       <c r="C10" t="str">
-        <v>DevOps &amp; Cloud</v>
+        <v>组织效能与绩效激活</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -870,7 +870,7 @@
         <v>91</v>
       </c>
       <c r="C11" t="str">
-        <v>DevOps &amp; Cloud</v>
+        <v>组织效能与绩效激活</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -884,7 +884,7 @@
         <v>95</v>
       </c>
       <c r="C12" t="str">
-        <v>Tools &amp; Others</v>
+        <v>人力数字化与用工合规</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>92</v>
       </c>
       <c r="C13" t="str">
-        <v>Tools &amp; Others</v>
+        <v>人力数字化与用工合规</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -912,7 +912,7 @@
         <v>86</v>
       </c>
       <c r="C14" t="str">
-        <v>Tools &amp; Others</v>
+        <v>人力数字化与用工合规</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -930,8 +930,8 @@
   <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
@@ -941,28 +941,28 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>编号</v>
       </c>
       <c r="B1" t="str">
-        <v>company</v>
+        <v>公司名称</v>
       </c>
       <c r="C1" t="str">
-        <v>role</v>
+        <v>职位</v>
       </c>
       <c r="D1" t="str">
-        <v>startDate</v>
+        <v>开始时间</v>
       </c>
       <c r="E1" t="str">
-        <v>endDate</v>
+        <v>结束时间</v>
       </c>
       <c r="F1" t="str">
-        <v>location</v>
+        <v>城市</v>
       </c>
       <c r="G1" t="str">
-        <v>description</v>
+        <v>工作描述（多条用 ; 分隔）</v>
       </c>
       <c r="H1" t="str">
-        <v>techStack</v>
+        <v>技能标签（多条用 ; 分隔）</v>
       </c>
     </row>
     <row r="2" ht="90" customHeight="1">
@@ -985,10 +985,10 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>多条工作描述用英文分号 ; 隔开</v>
+        <v>多条描述用英文分号 ; 隔开</v>
       </c>
       <c r="H2" t="str">
-        <v>多条技能标签用英文分号 ; 隔开</v>
+        <v>多条标签用英文分号 ; 隔开</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
@@ -1081,14 +1081,14 @@
   <dimension ref="A1:M5"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="45.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45.83203125" customWidth="1"/>
+    <col min="8" max="8" width="48.83203125" customWidth="1"/>
+    <col min="9" max="9" width="48.83203125" customWidth="1"/>
     <col min="10" max="10" width="55.83203125" customWidth="1"/>
     <col min="11" max="11" width="55.83203125" customWidth="1"/>
     <col min="12" max="12" width="55.83203125" customWidth="1"/>
@@ -1097,43 +1097,43 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>编号</v>
       </c>
       <c r="B1" t="str">
-        <v>title</v>
+        <v>项目名称</v>
       </c>
       <c r="C1" t="str">
-        <v>category</v>
+        <v>项目类别</v>
       </c>
       <c r="D1" t="str">
-        <v>featured</v>
+        <v>是否重点</v>
       </c>
       <c r="E1" t="str">
-        <v>role</v>
+        <v>项目角色</v>
       </c>
       <c r="F1" t="str">
-        <v>timeline</v>
+        <v>项目周期</v>
       </c>
       <c r="G1" t="str">
-        <v>description</v>
+        <v>项目简介</v>
       </c>
       <c r="H1" t="str">
-        <v>background</v>
+        <v>项目背景</v>
       </c>
       <c r="I1" t="str">
-        <v>objective</v>
+        <v>项目目标</v>
       </c>
       <c r="J1" t="str">
-        <v>actions</v>
+        <v>关键行动（多条用 ; 分隔）</v>
       </c>
       <c r="K1" t="str">
-        <v>outcomes</v>
+        <v>量化成果（多条用 ; 分隔）</v>
       </c>
       <c r="L1" t="str">
-        <v>highlights</v>
+        <v>亮点摘要（多条用 ; 分隔）</v>
       </c>
       <c r="M1" t="str">
-        <v>techStack</v>
+        <v>技术/方法论（多条用 ; 分隔）</v>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
@@ -1141,7 +1141,7 @@
         <v>📝 提示</v>
       </c>
       <c r="B2" t="str">
-        <v>featured 填 true 或 false</v>
+        <v>是否重点填: 是 或 否</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -1188,7 +1188,7 @@
         <v>薪酬福利核心工程</v>
       </c>
       <c r="D3" t="str">
-        <v>true</v>
+        <v>是</v>
       </c>
       <c r="E3" t="str">
         <v>项目负责人</v>
@@ -1229,7 +1229,7 @@
         <v>人力资源数字化</v>
       </c>
       <c r="D4" t="str">
-        <v>true</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
         <v>项目负责人</v>
@@ -1270,7 +1270,7 @@
         <v>组织能力盘点及发展</v>
       </c>
       <c r="D5" t="str">
-        <v>false</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
         <v>项目负责人</v>
@@ -1312,7 +1312,7 @@
   <dimension ref="A1:K3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
@@ -1326,37 +1326,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>编号</v>
       </c>
       <c r="B1" t="str">
-        <v>category</v>
+        <v>类别</v>
       </c>
       <c r="C1" t="str">
-        <v>institution</v>
+        <v>学校/机构</v>
       </c>
       <c r="D1" t="str">
-        <v>degree</v>
+        <v>学历</v>
       </c>
       <c r="E1" t="str">
-        <v>major</v>
+        <v>专业</v>
       </c>
       <c r="F1" t="str">
-        <v>startDate</v>
+        <v>开始时间</v>
       </c>
       <c r="G1" t="str">
-        <v>endDate</v>
+        <v>结束时间</v>
       </c>
       <c r="H1" t="str">
-        <v>certName</v>
+        <v>证书名称</v>
       </c>
       <c r="I1" t="str">
-        <v>certOrg</v>
+        <v>颁发机构</v>
       </c>
       <c r="J1" t="str">
-        <v>certDate</v>
+        <v>获证时间</v>
       </c>
       <c r="K1" t="str">
-        <v>highlights</v>
+        <v>亮点（多条用 ; 分隔）</v>
       </c>
     </row>
     <row r="2">
@@ -1446,10 +1446,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>key</v>
+        <v>配置项（勿改）</v>
       </c>
       <c r="B1" t="str">
-        <v>value</v>
+        <v>值（请修改这里）</v>
       </c>
     </row>
     <row r="2">
@@ -1457,7 +1457,7 @@
         <v>📝 填写说明</v>
       </c>
       <c r="B2" t="str">
-        <v>只修改右侧「值」列，左侧「配置项」列不要动</v>
+        <v>只修改本列，左侧配置项列不要动</v>
       </c>
     </row>
     <row r="3">

--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -622,7 +622,7 @@
         <v>name</v>
       </c>
       <c r="B3" t="str">
-        <v>陈晓敏</v>
+        <v>刘洋</v>
       </c>
     </row>
     <row r="4">
@@ -630,7 +630,7 @@
         <v>title</v>
       </c>
       <c r="B4" t="str">
-        <v>HRBP / 薪酬绩效资深专家</v>
+        <v>HRBP · 薪酬绩效专员</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>email</v>
       </c>
       <c r="B6" t="str">
-        <v>xiaomin.chen_hr@example.com</v>
+        <v>qmar1962@gmail.com</v>
       </c>
     </row>
     <row r="7">
@@ -654,7 +654,7 @@
         <v>phone</v>
       </c>
       <c r="B7" t="str">
-        <v>138-1234-5678</v>
+        <v>180-6234-4910</v>
       </c>
     </row>
     <row r="8">
@@ -662,7 +662,7 @@
         <v>location</v>
       </c>
       <c r="B8" t="str">
-        <v>中国 · 深圳</v>
+        <v>中国 · 武汉</v>
       </c>
     </row>
     <row r="9">
@@ -670,7 +670,7 @@
         <v>website</v>
       </c>
       <c r="B9" t="str">
-        <v>https://xiaomin-hrbp.github.io</v>
+        <v>https://qmar1962-cmd.github.io/interactive-visual-resume/</v>
       </c>
     </row>
     <row r="10">
@@ -678,7 +678,7 @@
         <v>github</v>
       </c>
       <c r="B10" t="str">
-        <v>xiaomin-hrbp</v>
+        <v>qmar1962-cmd</v>
       </c>
     </row>
     <row r="11">
@@ -686,7 +686,7 @@
         <v>linkedin</v>
       </c>
       <c r="B11" t="str">
-        <v>xiaomin-chen-hr</v>
+        <v>liuyang-hr</v>
       </c>
     </row>
     <row r="12">
@@ -694,7 +694,7 @@
         <v>bio</v>
       </c>
       <c r="B12" t="str">
-        <v>拥有 10 年+ 知名高成长科技企业及跨国集团深厚人力资源管理经验。专注于薪酬福利体系设计 (C&amp;B)、全面绩效激励闭环管理（OKR/KPI/三阶评估）以及业务合作伙伴 (HRBP) 战略落地。擅长将企业经营指标与人效分析指标深度绑定，通过精益调薪策略、宽带薪酬、多元激励以及人效诊断为业务部门打造高产出战队。</v>
+        <v>2 年物流运营中心薪酬绩效管理经验，主导华中大区近 9000 人绩效体系从计时制向计件制的全面转型。擅长将成本管控目标拆解为可执行的过程指标，通过数字化工具和人才梯队建设推动目标落地。喜欢用数据说话，也喜欢亲自下场做事。</v>
       </c>
     </row>
     <row r="13">
@@ -702,7 +702,7 @@
         <v>summary</v>
       </c>
       <c r="B13" t="str">
-        <v>高级人力资源管理师、资深 HRBP 专家。熟谙宽带薪酬、美世/海氏等标杆岗位技能要素评估体系，主导过多次覆盖千人规模的调薪与期权激励方案统筹；深挖业务核心痛点并进行组织重构设计与核心骨干盘点，具备极强的人效数据分析（People Analytics）与信息化 HR 治理工具落地应用能力。</v>
+        <v>主导过覆盖近 9000 人规模的计时转计件绩效方案落地，熟悉物流转运中心操作员岗位能力要素评估与单价测算体系；独立搭建 GPT 人工成本可视化平台（AI + Supabase + GitHub Pages），数据处理耗时压缩 67%；截至 2026 年 Q2，累计为大区节省人工成本 20 万+。</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +714,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -752,182 +752,112 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>宽带薪酬与定岗定级体系设计</v>
+        <v>绩效体系设计与落地（计时转计件）</v>
       </c>
       <c r="B3">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C3" t="str">
         <v>薪酬福利规划</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>全面绩效闭环与动态激励机制 (OKR/KPI)</v>
+        <v>人工成本预算分析与过程管控</v>
       </c>
       <c r="B4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C4" t="str">
         <v>薪酬福利规划</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>人工成本预算分析与总数控制 (C&amp;B Control)</v>
+        <v>单价测算与薪酬方案设计</v>
       </c>
       <c r="B5">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C5" t="str">
         <v>薪酬福利规划</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HRBP 业务诊断与组织痛点攻坚</v>
+        <v>效能盘点与人效数据分析</v>
       </c>
       <c r="B6">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C6" t="str">
-        <v>HRBP业务协同</v>
+        <v>组织效能与绩效激活</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>组织架构重建与核心岗位对标设计</v>
+        <v>绩效种子人才梯队培养</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" t="str">
-        <v>HRBP业务协同</v>
+        <v>组织效能与绩效激活</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>核心干部后备梯队盘点 (Succession Planning)</v>
+        <v>数据分析与可视化（Excel / PowerBI）</v>
       </c>
       <c r="B8">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="str">
-        <v>HRBP业务协同</v>
+        <v>人力数字化与用工合规</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>组织效能盘点与综合人效分析 (ROI &amp; L&amp;D)</v>
+        <v>AI辅助工具应用与低代码系统开发</v>
       </c>
       <c r="B9">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C9" t="str">
-        <v>组织效能与绩效激活</v>
+        <v>人力数字化与用工合规</v>
       </c>
       <c r="D9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>360度环评胜任力建模与反馈机制</v>
-      </c>
-      <c r="B10">
-        <v>88</v>
-      </c>
-      <c r="C10" t="str">
-        <v>组织效能与绩效激活</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>核心骨干定制激励与个人发展计划 (IDP)</v>
-      </c>
-      <c r="B11">
-        <v>91</v>
-      </c>
-      <c r="C11" t="str">
-        <v>组织效能与绩效激活</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>高级数据管理与决策透析 (Excel/PowerBI/SQL)</v>
-      </c>
-      <c r="B12">
-        <v>95</v>
-      </c>
-      <c r="C12" t="str">
-        <v>人力数字化与用工合规</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>一体化数智 HRM 与飞书 OKR 系统集成</v>
-      </c>
-      <c r="B13">
-        <v>92</v>
-      </c>
-      <c r="C13" t="str">
-        <v>人力数字化与用工合规</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>劳动纠纷防范与用工风险实务管理</v>
-      </c>
-      <c r="B14">
-        <v>86</v>
-      </c>
-      <c r="C14" t="str">
-        <v>人力数字化与用工合规</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -996,89 +926,38 @@
         <v>exp_1</v>
       </c>
       <c r="B3" t="str">
-        <v>领航创想智能科技有限公司</v>
+        <v>上海圆通蛟龙投资发展有限公司</v>
       </c>
       <c r="C3" t="str">
-        <v>资深 HRBP 专家 / 薪酬绩效部负责人</v>
+        <v>华中大区薪酬绩效专员</v>
       </c>
       <c r="D3" t="str">
-        <v>2022-04</v>
+        <v>2024-09</v>
       </c>
       <c r="E3" t="str">
         <v>至今</v>
       </c>
       <c r="F3" t="str">
-        <v>深圳</v>
+        <v>武汉</v>
       </c>
       <c r="G3" t="str">
-        <v>深度服务于千人级产研、运营及全球业务群。主导重构并落定了2023-2025年最新集团宽带薪酬标准和定岗定级总盘子，方案升级后，研发核心高价值人才流失率同比大幅缩减 35%。;打通'战略-绩效-激励'闭环，推行'OKR + 敏捷KPI双轨考核制'。协同产品线总裁重整核心业务提成与奖金分配政策，直接促成组织人效提升 18%，单兵销售业绩复合增长 22%。;联合数据团队从零构建'集团人效效能分析管理系统 (People Analytics Console)'，深度集成飞书与配薪核算引擎，实时打通人工成本支出额、编制冗余度、及绩效饱和度，为集团管委会决策提供精确数据依据。</v>
+        <v>人工成本预算与管控：Q1单次人工成本完成优于目标0.003元，完成率97%；1-2月单次人工分别低于目标0.004元、0.006元，3月达成目标；截至5月，大区累计节余成本超20万元。;绩效体系落地推进：截至Q2，累计推动13个中心上线（武汉、襄阳、长沙、赣州、新乡、郑州、漯河、荆州、横峰、武昌、衡阳、常德、南昌），绩效上线率达94%。;AI人工成本诊断工具部署：搭建GPT人工成本异常诊断机制，部署线上可视化平台，推动中心日常用工管理精细化。;绩效种子人才培养：构建中心绩效人才全流程培养体系（理论培训→现场实操→汇报认证），2025年累计培养绩效人员13人，通过率100%，优秀率54%（7人）；2026年Q1再培养9人。</v>
       </c>
       <c r="H3" t="str">
-        <v>全面薪酬宽带管理 (C&amp;B);组织架构重组;OKR/KPI 双轨考核制;人效看板 (BI);飞书HRM;中高管绩效辅导</v>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="str">
-        <v>exp_2</v>
-      </c>
-      <c r="B4" t="str">
-        <v>极光数字空间科技有限公司</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HRBP 经理 (产研事业部负责人)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2018-09</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2022-03</v>
-      </c>
-      <c r="F4" t="str">
-        <v>深圳</v>
-      </c>
-      <c r="G4" t="str">
-        <v>全面负责技术中心（450人+）的组织发展、人才梯队与激励配置工作。主导中高层核心中坚力量两轮大盘点，并对核心核心架构师及骨干实施'一人一策'动态股权保留政策，使核心技术专家留任率提升至 95%。;深入业务核心开展敏捷改组，剥离重叠的多维繁冗层级，重组为 8 个高内聚自闭环业务战队，大幅提升内部业务流转与人效提速 15%。;推行月度人效专项复盘、新晋技术经理管理辅导；协同集团年度薪酬回顾，解决历史不匹配倒挂等痛点，年度调薪满意度评分达 4.8 / 5.0。</v>
-      </c>
-      <c r="H4" t="str">
-        <v>HRBP 实践;胜任力模型评估;晋升评审机制;晋升调薪测算模型;组织诊断与人效分析</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>exp_3</v>
-      </c>
-      <c r="B5" t="str">
-        <v>中科智能制造控股集团</v>
-      </c>
-      <c r="C5" t="str">
-        <v>人力资源主管 -&gt; 薪酬福利高级专员</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2015-07</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2018-08</v>
-      </c>
-      <c r="F5" t="str">
-        <v>上海</v>
-      </c>
-      <c r="G5" t="str">
-        <v>统管 2000+ 关系复杂中大型组织员工算薪、多层级社保公积金及个税代扣代缴事宜，流程精密核算，创下连续 12 季度 100% 算薪'零差错'。;深度协助美世（Mercer）岗位对标盘点咨询项目，作为项目主力撰写与对标 150 余个核心中高层及技术研发关键岗位说明书；协同定制《集团薪酬福利精益发放白皮书》，极大降低不规避福利成本支出。</v>
-      </c>
-      <c r="H5" t="str">
-        <v>海氏/美世岗位对标;精密个税社保算薪实务;用工风险管理;组织绩效模型;高级 Excel 分析建模</v>
-      </c>
-    </row>
+        <v>绩效方案设计与落地;人效数据分析;人才梯队建设;成本管控</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1"/>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -1182,10 +1061,10 @@
         <v>proj_1</v>
       </c>
       <c r="B3" t="str">
-        <v>最新年度全集团宽带薪酬重构及动态绩效挂钩计划</v>
+        <v>全员绩效线上化推进</v>
       </c>
       <c r="C3" t="str">
-        <v>薪酬福利核心工程</v>
+        <v>绩效</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -1194,28 +1073,28 @@
         <v>项目负责人</v>
       </c>
       <c r="F3" t="str">
-        <v>2023-2024</v>
+        <v>2025.3—2026.8</v>
       </c>
       <c r="G3" t="str">
-        <v>针对原有薪金重合严重、职级虚高、起步倒挂等历史痛点，主导落地的涵盖千人规模的宽带薪酬重新评估定档和调薪算法项目。</v>
+        <v>响应公司「人人有绩效，事事讲绩效」战略，聚焦操作员绩效体系优化，通过「操作量+效率+质量」三维关联薪酬，推动员工从「要你做」向「我要做」转变，实现降本、增效、提质。</v>
       </c>
       <c r="H3" t="str">
-        <v>原有薪酬体系存在薪金重合严重、职级虚高、起步倒挂等历史痛点，导致核心人才流失率高、调薪满意度低，亟需系统性重构。</v>
+        <v>转运中心原有绩效方案存在不公平、不透明、无激励效果、起步倒挂等问题，需主导近9000人规模的绩效模型重建与计时转计件切换。</v>
       </c>
       <c r="I3" t="str">
-        <v>在把控总人本支出增幅低于5%的前提下，激活绩优主力团队，同时消除历史倒挂问题。</v>
+        <v>降本增效，过程公开透明，让员工感受到努力有回报。</v>
       </c>
       <c r="J3" t="str">
-        <v>搭建深度仿真数学测算，推演12种不同调薪分配曲线，量化分析每种方案的成本影响与激励效果。;引入美世（Mercer）岗位要素评估体系，对全集团核心岗位重新定档定级。;设计晋升定级和薪资起锚点的自动锁定矩阵，实现调薪流程标准化与自动化。</v>
+        <v>搭建绩效种子人才梯队：人员筛选→分模块培训→实操交付物验收→线上测试与汇报认证，全链路闭环。;绩效推进目标数字化：贯彻32项核心指标，分23步有序推进，过程全程可视化追踪。</v>
       </c>
       <c r="K3" t="str">
-        <v>在把控总人本支出增幅低于5%的同时，高质激活了前40%的绩优主力团队。;将历史倒挂严重性由25%压缩至2.5%以内。;研发核心高价值人才流失率同比大幅缩减35%。</v>
+        <v>截至2026年Q2，累计推动13个中心上线（武汉、襄阳、长沙、赣州、新乡、郑州、漯河、荆州、横峰、武昌、衡阳、常德、南昌），绩效上线率达94%。</v>
       </c>
       <c r="L3" t="str">
-        <v>搭建深度仿真数学测算，推演 12 种不同调薪分配曲线，最终实现在把控总人本支出增幅低于 5% 的同时，高质激活了前 40% 的绩优主力团队。;重置新晋升定级和薪资起锚点的自动锁定矩阵，将历史倒挂严重性由 25% 压缩至 2.5% 以内。</v>
+        <v>先在中心培养一批深入一线、懂业务的绩效种子，再用他们推动项目落地——这比空降推进员快得多，也稳得多。;推进过程贯彻「先了解业务才能推动业务」原则，32项指标+23个步骤全程数字化监控，进度一目了然。</v>
       </c>
       <c r="M3" t="str">
-        <v>宽带薪酬;调薪矩阵算法;美世定档模型;Excel 仿真财务模型</v>
+        <v>人才梯队建设;绩效方案设计;目标数字化管理</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -1223,40 +1102,40 @@
         <v>proj_2</v>
       </c>
       <c r="B4" t="str">
-        <v>HR 人效数据飞轮与"一站式人效监控 BI 决策平台"</v>
+        <v>绩效种子人才培养体系</v>
       </c>
       <c r="C4" t="str">
-        <v>人力资源数字化</v>
+        <v>人才</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
         <v>项目负责人</v>
       </c>
       <c r="F4" t="str">
-        <v>2023-2024</v>
+        <v>2025.4—2026.6</v>
       </c>
       <c r="G4" t="str">
-        <v>自研一套与飞书多维表格与 PowerBI 打通的组织效能监控系统，用于全息透视实时人员编制、主动流失、业绩 ROI、单兵创出以及绩效偏离系数。</v>
+        <v>为中区各中心绩效推进提供本地化人才支撑，解决「没有合适的人来推」的根本问题。</v>
       </c>
       <c r="H4" t="str">
-        <v>传统人力数据统计依赖手工跨源取数，效率低下且时效性差，管理层无法实时获取人效数据支撑决策。</v>
+        <v>中区14个中心全面推行绩效改革，但各中心缺乏既懂绩效又熟悉现场的执行人员。</v>
       </c>
       <c r="I4" t="str">
-        <v>将人效数据从手工两周合并一次升级为日级自动抓取，构建实时组织效能监控与预警体系。</v>
+        <v>14个中心各培养1-2名能独立推进绩效工作的本地种子。</v>
       </c>
       <c r="J4" t="str">
-        <v>打通飞书多维表格与PowerBI数据流，建立自动化数据采集与清洗管道。;设计组织效能指标库，涵盖人员编制、主动流失率、业绩ROI、单兵产出、绩效偏离系数等核心维度。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标等智能预警模型。</v>
+        <v>精准选人：分两类人员定向招募——中心人资（懂薪酬基础、有数据能力）和中心新锐生（懂现场、学得快），面试通过后再定是否使用。;分模块培训：每模块结束需完成对应实操任务，理论与实践同步推进，确保学了能用。</v>
       </c>
       <c r="K4" t="str">
-        <v>将传统手工跨源取数及算账时间从两周合并一次缩短至日级自动抓取更新，人力统计生产力提升95%。;帮助管理层提早识别并化解多起用工重叠危机，避免潜在成本损失。;实时数据看板覆盖全集团，管委会决策响应速度提升3倍。</v>
+        <v>截至2026年5月，中区14个中心共22名绩效种子通过总部认证，通过率100%，10人荣获「优秀」，优秀率68%。</v>
       </c>
       <c r="L4" t="str">
-        <v>将传统手工跨源取数及算账的时间从原本每两周合并一次缩短至日级自动抓取更新，提高人力资源统计生产力达 95%。;融入组织规模预膨胀系数、核心异动预警、绩优被动流失危机指标，帮助管理层提早识别并化解了多起用工重叠危机。</v>
+        <v>先面试再用人，两类人员配不同培训计划，避免一刀切。;培训中理论与实操并重，交付物验收+测试汇报双重把关，培养出来的人真正可用。</v>
       </c>
       <c r="M4" t="str">
-        <v>PowerBI;People Analytics;数据清洗;指标库治理;飞书 API</v>
+        <v>人才精准匹配;现场培训体系;方案落地验收</v>
       </c>
     </row>
     <row r="5">
@@ -1264,45 +1143,86 @@
         <v>proj_3</v>
       </c>
       <c r="B5" t="str">
-        <v>产研核心主管 360 度能力盘点与"主管成长加速营"</v>
+        <v>人工成本管控体系建设</v>
       </c>
       <c r="C5" t="str">
-        <v>组织能力盘点及发展</v>
+        <v>成本</v>
       </c>
       <c r="D5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E5" t="str">
         <v>项目负责人</v>
       </c>
       <c r="F5" t="str">
-        <v>2022-2023</v>
+        <v>2025.3—至今</v>
       </c>
       <c r="G5" t="str">
-        <v>针对产研事业部中层管理者管理成熟度参差不齐的问题，引入针对性的 360 度胜任力矩阵全方位诊断，并配套设计出 IDP (个人成长计划) 落地赋能方案。</v>
+        <v>在全员绩效落地后，将成本管控的抓手从结果向过程迁移，实现日周月全链路精细化管控。</v>
       </c>
       <c r="H5" t="str">
-        <v>产研事业部中层管理者管理成熟度参差不齐，基层工程师与管理者沟通割裂，内部继任准备度不足。</v>
+        <v>绩效推进完成后，年度成本压力加大，管控重心需从结果核算转向过程干预。</v>
       </c>
       <c r="I5" t="str">
-        <v>通过360度胜任力诊断精准定位管理短板，配套IDP个人成长计划与加速营，提升内部继任准备度。</v>
+        <v>人工成本与人效目标双达成。</v>
       </c>
       <c r="J5" t="str">
-        <v>引入360度胜任力矩阵，对80+中高级经理进行全方位能力诊断与盘点。;基于诊断结果，为核心高潜人才设计'一人一策'IDP个人发展计划。;配套两场'管理者角色转身理论与研讨'，聚焦沟通力与团队领导力提升。</v>
+        <v>前置预算管理：每月底对本月开销复盘并锁定下月预算，过程中每周回顾，及时调整。;每日精细化排班：货量淡季摸排最低用工标准，人资现场稽核。;单价月度调整：保障岗位效能偏差控制在10%以内，每月按时发起单价调整100%执行。</v>
       </c>
       <c r="K5" t="str">
-        <v>高标准全票落地80+中高级经理能力诊断，构建核心高潜力人才蓄水池。;组织'内部继任准备度'实质性提升40%。;基层工程师与管理者沟通满意度显著改善。</v>
+        <v>人均效能：2024年1748→2025年1974→2026年2107，逐年提升。;单次人工成本：2024年0.0105→2025年0.0091→2026年0.0088，稳步下降。;截至5月，大区累计节余人工成本超20万元。</v>
       </c>
       <c r="L5" t="str">
-        <v>高标准全票落地 80+ 中高级经理能力诊断，构建集团核心高潜力人才蓄水池，使组织'内部继任准备度'实质提升 40%。;配套两场'管理者角色转身理论与研讨'，切实改善了产研线基层工程师与管理者之间原本割裂的沟通习惯。</v>
+        <v>单价调整每月按时发起，执行率100%，没有一次延误。;用前置预算代替事后算账，把问题消灭在萌芽阶段。</v>
       </c>
       <c r="M5" t="str">
-        <v>360度评估机制;胜任力九宫格;IDP 提升路线;管理者角色转身辅导</v>
+        <v>日周月闭环管理;前置预算管理;精细化排班</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>proj_4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>AI辅助人工成本可视化平台</v>
+      </c>
+      <c r="C6" t="str">
+        <v>数字化</v>
+      </c>
+      <c r="D6" t="str">
+        <v>否</v>
+      </c>
+      <c r="E6" t="str">
+        <v>项目负责人</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2025.11—至今</v>
+      </c>
+      <c r="G6" t="str">
+        <v>借助AI工具自主开发GPT线上看板，对人工成本异常数据做二次加工，形成常态化监控看板并实现部分指标前置预警。</v>
+      </c>
+      <c r="H6" t="str">
+        <v>GPT数据已纳入人资季度KPI考核，原有手工处理模式耗时长、易出错，且无法实时共享，影响团队协同效率。</v>
+      </c>
+      <c r="I6" t="str">
+        <v>GPT预警提前介入，看板实时可监控、可追溯历史数据。</v>
+      </c>
+      <c r="J6" t="str">
+        <v>梳理数据口径形成标准数据表，使用Claude Code进行系统开发，Supabase搭建云数据库支持多人协同，GitHub Pages完成线上部署。</v>
+      </c>
+      <c r="K6" t="str">
+        <v>数据处理耗时从30分钟压缩至10分钟核验即可发布，效率提升67%。;出勤预警提前从15天→10天，缺勤预警从7天→5天，留出更多排班调整空间。;告别单人单机流转文件，支持团队多人在线协同编辑。</v>
+      </c>
+      <c r="L6" t="str">
+        <v>借助AI低代码工具自主完成从数据库到线上部署的全栈开发，零外包依赖，自主可控。;报表自动化渲染，数据处理效率提升67%，人力成本显著降低。</v>
+      </c>
+      <c r="M6" t="str">
+        <v>AI辅助开发（Claude Code）;Supabase云数据库;GitHub Pages部署</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1402,19 +1322,19 @@
         <v>学历教育</v>
       </c>
       <c r="C3" t="str">
-        <v>中南财经政法大学</v>
+        <v>武汉纺织大学</v>
       </c>
       <c r="D3" t="str">
         <v>本科</v>
       </c>
       <c r="E3" t="str">
-        <v>人力资源管理</v>
+        <v>环境设计</v>
       </c>
       <c r="F3" t="str">
-        <v>2011-09</v>
+        <v>2020-09</v>
       </c>
       <c r="G3" t="str">
-        <v>2015-06</v>
+        <v>2024-06</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -1426,7 +1346,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>主修组织行为学、薪酬福利设计、绩效考评与实务、劳动法与合同合规规划。;曾荣获国家级励志奖学金、校级优秀毕业生。毕设《互联网科技企业动态期权及虚拟股绩效绑定设计》被评为校级一等论文。</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1465,7 +1385,7 @@
         <v>username</v>
       </c>
       <c r="B3" t="str">
-        <v>xiaomin-hrbp</v>
+        <v>qmar1962-cmd</v>
       </c>
     </row>
     <row r="4">
@@ -1481,7 +1401,7 @@
         <v>repoCountOverride</v>
       </c>
       <c r="B5" t="str">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1489,7 +1409,7 @@
         <v>commitCountOverride</v>
       </c>
       <c r="B6" t="str">
-        <v>184</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -1497,7 +1417,7 @@
         <v>starredCountOverride</v>
       </c>
       <c r="B7" t="str">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1505,7 +1425,7 @@
         <v>languages</v>
       </c>
       <c r="B8" t="str">
-        <v>薪酬福利设计与规划 (C&amp;B):38.5:#10b981;全面绩效激励机制对齐 (KPI/OKR):28.2:#3b82f6;HRBP 业务诊断与组织发展 (OD):18.3:#f59e0b;人效效能分析系统 (BI &amp; Analytics):10.0:#8b5cf6;劳动合同合规与用工风险预防:5.0:#ef4444</v>
+        <v>绩效体系设计与落地:38.5:#10b981;人工成本管控:28.2:#3b82f6;人效数据分析:18.3:#f59e0b;AI工具应用与数字化:15.0:#8b5cf6</v>
       </c>
     </row>
   </sheetData>

--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -638,7 +638,7 @@
         <v>avatarUrl</v>
       </c>
       <c r="B5" t="str">
-        <v>https://images.unsplash.com/photo-1573496359142-b8d87734a5a2?auto=format&amp;fit=crop&amp;q=80&amp;w=200&amp;h=200</v>
+        <v>/avatar.jpg</v>
       </c>
     </row>
     <row r="6">

--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -638,7 +638,7 @@
         <v>avatarUrl</v>
       </c>
       <c r="B5" t="str">
-        <v>/avatar.jpg</v>
+        <v>/interactive-visual-resume/avatar.jpg</v>
       </c>
     </row>
     <row r="6">

--- a/resume-data.xlsx
+++ b/resume-data.xlsx
@@ -630,7 +630,7 @@
         <v>title</v>
       </c>
       <c r="B4" t="str">
-        <v>HRBP · 薪酬绩效专员</v>
+        <v>薪酬绩效推进 · 人工成本管控</v>
       </c>
     </row>
     <row r="5">
@@ -694,7 +694,7 @@
         <v>bio</v>
       </c>
       <c r="B12" t="str">
-        <v>2 年物流运营中心薪酬绩效管理经验，主导华中大区近 9000 人绩效体系从计时制向计件制的全面转型。擅长将成本管控目标拆解为可执行的过程指标，通过数字化工具和人才梯队建设推动目标落地。喜欢用数据说话，也喜欢亲自下场做事。</v>
+        <v>2年物流运营中心薪酬绩效管理经验，统筹华中大区14个中心约20名绩效专员，推进覆盖近9000名操作工的全员绩效改革（计时转计件）。擅长将成本管控目标拆解为可执行的过程指标，通过数字化工具和人才梯队建设推动目标落地。喜欢用数据说话，也喜欢亲自下场做事。求职意向：HRBP / 薪酬绩效管理。</v>
       </c>
     </row>
     <row r="13">
@@ -702,7 +702,7 @@
         <v>summary</v>
       </c>
       <c r="B13" t="str">
-        <v>主导过覆盖近 9000 人规模的计时转计件绩效方案落地，熟悉物流转运中心操作员岗位能力要素评估与单价测算体系；独立搭建 GPT 人工成本可视化平台（AI + Supabase + GitHub Pages），数据处理耗时压缩 67%；截至 2026 年 Q2，累计为大区节省人工成本 20 万+。</v>
+        <v>统筹14个中心约20名绩效专员推进全员绩效改革落地，熟悉物流转运中心操作员岗位能力要素评估与单价测算体系；独立搭建GPT人工成本可视化平台（AI + Supabase + GitHub Pages），数据处理耗时压缩67%；2026年1-5月，通过每月单价调整累计节余人工成本超20万元。</v>
       </c>
     </row>
   </sheetData>
@@ -738,7 +738,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>📝 分类对照: 薪酬福利规划=Frontend | HRBP业务协同=Backend | 组织效能与绩效激活=DevOps &amp; Cloud | 人力数字化与用工合规=Tools &amp; Others</v>
+        <v>📝 分类填: 薪酬福利规划 / HRBP业务协同 / 组织效能与绩效激活 / 人力数字化与用工合规</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -929,7 +929,7 @@
         <v>上海圆通蛟龙投资发展有限公司</v>
       </c>
       <c r="C3" t="str">
-        <v>华中大区薪酬绩效专员</v>
+        <v>华中大区薪酬绩效专员（统筹推进）</v>
       </c>
       <c r="D3" t="str">
         <v>2024-09</v>
@@ -941,7 +941,7 @@
         <v>武汉</v>
       </c>
       <c r="G3" t="str">
-        <v>人工成本预算与管控：Q1单次人工成本完成优于目标0.003元，完成率97%；1-2月单次人工分别低于目标0.004元、0.006元，3月达成目标；截至5月，大区累计节余成本超20万元。;绩效体系落地推进：截至Q2，累计推动13个中心上线（武汉、襄阳、长沙、赣州、新乡、郑州、漯河、荆州、横峰、武昌、衡阳、常德、南昌），绩效上线率达94%。;AI人工成本诊断工具部署：搭建GPT人工成本异常诊断机制，部署线上可视化平台，推动中心日常用工管理精细化。;绩效种子人才培养：构建中心绩效人才全流程培养体系（理论培训→现场实操→汇报认证），2025年累计培养绩效人员13人，通过率100%，优秀率54%（7人）；2026年Q1再培养9人。</v>
+        <v>统筹华中大区14个中心约20名绩效专员，推进覆盖近9000名操作工的全员绩效改革。;人工成本预算与管控：Q1单次人工成本完成优于目标0.003元，完成率97%；1-2月单次人工分别低于目标0.004元、0.006元，3月达成目标；2026年1-5月通过每月单价调整累计节余成本超20万元。;绩效体系落地推进：截至Q2，累计推动13个中心上线（武汉、襄阳、长沙、赣州、新乡、郑州、漯河、荆州、横峰、武昌、衡阳、常德、南昌），绩效上线率达94%。;AI人工成本诊断工具部署：搭建GPT人工成本异常诊断机制，部署线上可视化平台，推动中心日常用工管理精细化。;绩效种子人才培养：构建中心绩效人才全流程培养体系（理论培训→现场实操→汇报认证），2025年累计培养绩效人员13人，通过率100%，优秀率54%（7人）；2026年Q1再培养9人。</v>
       </c>
       <c r="H3" t="str">
         <v>绩效方案设计与落地;人效数据分析;人才梯队建设;成本管控</v>
@@ -1170,7 +1170,7 @@
         <v>前置预算管理：每月底对本月开销复盘并锁定下月预算，过程中每周回顾，及时调整。;每日精细化排班：货量淡季摸排最低用工标准，人资现场稽核。;单价月度调整：保障岗位效能偏差控制在10%以内，每月按时发起单价调整100%执行。</v>
       </c>
       <c r="K5" t="str">
-        <v>人均效能：2024年1748→2025年1974→2026年2107，逐年提升。;单次人工成本：2024年0.0105→2025年0.0091→2026年0.0088，稳步下降。;截至5月，大区累计节余人工成本超20万元。</v>
+        <v>人均效能：2024年1748→2025年1974→2026年2107，逐年提升。;单次人工成本：2024年0.0105→2025年0.0091→2026年0.0088，稳步下降。;2026年1-5月，通过每月单价调整累计节余人工成本超20万元。</v>
       </c>
       <c r="L5" t="str">
         <v>单价调整每月按时发起，执行率100%，没有一次延误。;用前置预算代替事后算账，把问题消灭在萌芽阶段。</v>
@@ -1346,7 +1346,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>毕业后加入圆通，从业务一线转型至薪酬绩效管理，在实操中快速建立专业能力</v>
       </c>
     </row>
   </sheetData>
